--- a/output/pdf_financials_xlsx/LXM.xlsx
+++ b/output/pdf_financials_xlsx/LXM.xlsx
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.075614</v>
+        <v>-0.075614</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.37544</v>
+        <v>-0.37544</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.209213</v>
+        <v>-0.209213</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.199624</v>
+        <v>-0.199624</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.575236</v>
@@ -1420,16 +1420,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.075614</v>
+        <v>-0.075614</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.37544</v>
+        <v>-0.37544</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.209213</v>
+        <v>-0.209213</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.199624</v>
+        <v>-0.199624</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.575236</v>
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.075614</v>
+        <v>-0.075614</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.37544</v>
+        <v>-0.37544</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.209213</v>
+        <v>-0.209213</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.199624</v>
+        <v>-0.199624</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.575236</v>
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.520467</v>
+        <v>2.520467</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-6.257333</v>
+        <v>6.257333</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-10.46065</v>
+        <v>10.46065</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-9.981199999999999</v>
+        <v>9.981199999999999</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>1.554692</v>
@@ -1777,16 +1777,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.075614</v>
+        <v>-0.075614</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.37544</v>
+        <v>-0.37544</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.209213</v>
+        <v>-0.209213</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.199624</v>
+        <v>-0.199624</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.575236</v>
@@ -1879,16 +1879,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.075614</v>
+        <v>-0.075614</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.37544</v>
+        <v>-0.37544</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.209213</v>
+        <v>-0.209213</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.199624</v>
+        <v>-0.199624</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.575236</v>
@@ -2007,16 +2007,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -5283,16 +5283,16 @@
         <v>2.63988</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.909991</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.909991</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.909991</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.129713</v>
       </c>
     </row>
     <row r="93">
@@ -6580,43 +6580,43 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.08469500000000001</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.165908</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.279398</v>
+        <v>0.278189</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>3.52407</v>
+        <v>1.930246</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>6.202629</v>
+        <v>5.901619</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.801441</v>
+        <v>0.442856</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>5.891907</v>
+        <v>-1.773369</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>7.003643</v>
+        <v>5.342047</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>6.520539</v>
+        <v>6.458744</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.2</v>
+        <v>0.156655</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.1048</v>
+        <v>0.036681</v>
       </c>
     </row>
     <row r="119">
@@ -8366,7 +8366,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -9066,7 +9070,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -9998,7 +10006,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -13690,7 +13702,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -15460,7 +15476,11 @@
           <t>Exploration and evaluation asset expenditures, net</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -17536,7 +17556,11 @@
           <t>Exploration and evaluation asset expenditures, net</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -19008,7 +19032,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -28664,13 +28692,13 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>0.37544</v>
+        <v>-0.37544</v>
       </c>
       <c r="H250" s="5" t="n">
-        <v>0.209213</v>
+        <v>-0.209213</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>0.199624</v>
+        <v>-0.199624</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -29951,10 +29979,10 @@
         </is>
       </c>
       <c r="F265" s="5" t="n">
-        <v>0.075614</v>
+        <v>-0.075614</v>
       </c>
       <c r="G265" s="5" t="n">
-        <v>0.37544</v>
+        <v>-0.37544</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LXM.xlsx
+++ b/output/pdf_financials_xlsx/LXM.xlsx
@@ -984,19 +984,19 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.005832</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000738</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000971</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000873</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000389</v>
       </c>
     </row>
     <row r="13">
@@ -1801,19 +1801,19 @@
         <v>-1.193997</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.655707</v>
+        <v>-2.661539</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.466764</v>
+        <v>-8.467502</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.941498</v>
+        <v>-6.942469</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.300703</v>
+        <v>-0.301576</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.855046</v>
+        <v>-0.8554349999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1903,19 +1903,19 @@
         <v>-1.193997</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.655707</v>
+        <v>-2.661539</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-8.466764</v>
+        <v>-8.467502</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.941498</v>
+        <v>-6.942469</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.300703</v>
+        <v>-0.301576</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.855046</v>
+        <v>-0.8554349999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2142,25 +2142,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.024975</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.146757</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.093499</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.00017</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.178018</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.260836</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.042653</v>
@@ -2172,13 +2172,13 @@
         <v>0.191069</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.035728</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.003439</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.207927</v>
       </c>
     </row>
     <row r="35">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.024975</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.146757</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.093499</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.00017</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.178018</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.260836</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.042653</v>
@@ -2274,13 +2274,13 @@
         <v>0.191069</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.13194</v>
+        <v>0.167668</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.0112</v>
+        <v>0.014639</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.0176</v>
+        <v>0.225527</v>
       </c>
     </row>
     <row r="37">
@@ -2856,25 +2856,25 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.024975</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.146757</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.093499</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.00019</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.00017</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.189905</v>
+        <v>0.011887</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.340372</v>
+        <v>0.079536</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.02522</v>
@@ -2886,13 +2886,13 @@
         <v>0.024325</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.057042</v>
+        <v>0.021314</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.021793</v>
+        <v>0.018354</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.228284</v>
+        <v>0.020357</v>
       </c>
     </row>
     <row r="49">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">

--- a/output/pdf_financials_xlsx/LXM.xlsx
+++ b/output/pdf_financials_xlsx/LXM.xlsx
@@ -5713,16 +5713,16 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.001476</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.033187</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.032927</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.001649</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>-0.006274</v>
@@ -5749,7 +5749,7 @@
         <v>-0.00025</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002899</v>
       </c>
     </row>
     <row r="102">
@@ -5968,16 +5968,16 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.001115</v>
+        <v>0.002591</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.102154</v>
+        <v>0.068967</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.009028</v>
+        <v>0.041955</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.040997</v>
+        <v>-0.039348</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0.169227</v>
@@ -6004,7 +6004,7 @@
         <v>0.034823</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.185136</v>
+        <v>-0.188035</v>
       </c>
     </row>
     <row r="107">
@@ -6457,10 +6457,10 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.110682</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.192593</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -13316,7 +13316,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -13788,7 +13792,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -14050,7 +14058,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -19204,7 +19216,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -20852,7 +20868,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -21022,7 +21042,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
